--- a/tarifas_logisticas.xlsx
+++ b/tarifas_logisticas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/50db0a26be1b61d4/Documentos/Claude/Projects/LOGÍSTICA/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/50db0a26be1b61d4/Documentos/GitHub/Optimizador-log-stico/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="266" documentId="11_391E9D1A9AA9BC629EC0B7D49EF19998B2D3ECC3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{105AA0D4-7059-4EC6-9D67-DFD364761DAA}"/>
+  <xr:revisionPtr revIDLastSave="268" documentId="11_391E9D1A9AA9BC629EC0B7D49EF19998B2D3ECC3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF00ECF4-6443-4C44-92B2-A4D92EBF043C}"/>
   <bookViews>
-    <workbookView xWindow="3180" yWindow="1704" windowWidth="17280" windowHeight="8880" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INSTRUCCIONES" sheetId="1" r:id="rId1"/>
@@ -799,10 +799,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1269,6 +1265,7 @@
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="14.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
